--- a/reference/origins/product info/Concentrate Final Product List for WA.xlsx
+++ b/reference/origins/product info/Concentrate Final Product List for WA.xlsx
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConcentratesTable" displayName="ConcentratesTable" ref="A1:N51" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ConcentratesTable" displayName="ConcentratesTable" ref="A1:N61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Brand"/>
@@ -2697,6 +2697,446 @@
       </x:c>
       <x:c r="O51"/>
     </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="10" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B52" s="10" t="str">
+        <x:v>Skord</x:v>
+      </x:c>
+      <x:c r="C52" s="10" t="str">
+        <x:v>Blue Dream</x:v>
+      </x:c>
+      <x:c r="D52" s="10" t="str">
+        <x:v>Kief</x:v>
+      </x:c>
+      <x:c r="E52" s="10" t="str">
+        <x:v>Loose Kief</x:v>
+      </x:c>
+      <x:c r="F52" s="10" t="str">
+        <x:v>Hybrid</x:v>
+      </x:c>
+      <x:c r="G52" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H52" s="14" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I52" s="10" t="str">
+        <x:v>48.6</x:v>
+      </x:c>
+      <x:c r="J52" s="10" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K52" s="12" t="str">
+        <x:v>Finely sifted Blue Dream trichomes carry soft earth, fresh pine and peppery spice, ready for topping a bowl or boosting a joint.</x:v>
+      </x:c>
+      <x:c r="L52" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+      <x:c r="M52" s="12" t="str">
+        <x:v>Pinene</x:v>
+      </x:c>
+      <x:c r="N52" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="10" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B53" s="10" t="str">
+        <x:v>Plaid Jacket</x:v>
+      </x:c>
+      <x:c r="C53" s="10" t="str">
+        <x:v>Jack Herer</x:v>
+      </x:c>
+      <x:c r="D53" s="10" t="str">
+        <x:v>Kief</x:v>
+      </x:c>
+      <x:c r="E53" s="10" t="str">
+        <x:v>Loose Kief</x:v>
+      </x:c>
+      <x:c r="F53" s="10" t="str">
+        <x:v>Sativa</x:v>
+      </x:c>
+      <x:c r="G53" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H53" s="14" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I53" s="10" t="str">
+        <x:v>46.9</x:v>
+      </x:c>
+      <x:c r="J53" s="10" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K53" s="12" t="str">
+        <x:v>Loose kief with the bright, herbal lift Jack Herer is known for, pine-forward and clean across the whole sift.</x:v>
+      </x:c>
+      <x:c r="L53" s="12" t="str">
+        <x:v>Terpinolene</x:v>
+      </x:c>
+      <x:c r="M53" s="12" t="str">
+        <x:v>Pinene</x:v>
+      </x:c>
+      <x:c r="N53" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="10" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B54" s="10" t="str">
+        <x:v>Refine</x:v>
+      </x:c>
+      <x:c r="C54" s="10" t="str">
+        <x:v>Permanent Marker</x:v>
+      </x:c>
+      <x:c r="D54" s="10" t="str">
+        <x:v>Kief</x:v>
+      </x:c>
+      <x:c r="E54" s="10" t="str">
+        <x:v>Dry Sift Kief</x:v>
+      </x:c>
+      <x:c r="F54" s="10" t="str">
+        <x:v>Hybrid</x:v>
+      </x:c>
+      <x:c r="G54" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H54" s="14" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I54" s="10" t="str">
+        <x:v>51.4</x:v>
+      </x:c>
+      <x:c r="J54" s="10" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K54" s="12" t="str">
+        <x:v>Traditional dry sift with a bold, gassy nose - peppery spice up front, citrus and sweet earth behind it.</x:v>
+      </x:c>
+      <x:c r="L54" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+      <x:c r="M54" s="12" t="str">
+        <x:v>Limonene</x:v>
+      </x:c>
+      <x:c r="N54" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="10" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B55" s="10" t="str">
+        <x:v>Dank Czar</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="str">
+        <x:v>Wedding Cake</x:v>
+      </x:c>
+      <x:c r="D55" s="10" t="str">
+        <x:v>Kief</x:v>
+      </x:c>
+      <x:c r="E55" s="10" t="str">
+        <x:v>Dry Sift Kief</x:v>
+      </x:c>
+      <x:c r="F55" s="10" t="str">
+        <x:v>Indica Hybrid</x:v>
+      </x:c>
+      <x:c r="G55" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H55" s="14" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I55" s="10" t="str">
+        <x:v>53.2</x:v>
+      </x:c>
+      <x:c r="J55" s="10" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K55" s="12" t="str">
+        <x:v>Dense, sugary dry sift pressed from Wedding Cake, layering citrus, warm spice and a doughy sweetness.</x:v>
+      </x:c>
+      <x:c r="L55" s="12" t="str">
+        <x:v>Limonene</x:v>
+      </x:c>
+      <x:c r="M55" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+      <x:c r="N55" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="10" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B56" s="10" t="str">
+        <x:v>Buddies</x:v>
+      </x:c>
+      <x:c r="C56" s="10" t="str">
+        <x:v>ACDC</x:v>
+      </x:c>
+      <x:c r="D56" s="10" t="str">
+        <x:v>Kief</x:v>
+      </x:c>
+      <x:c r="E56" s="10" t="str">
+        <x:v>Infused Kief</x:v>
+      </x:c>
+      <x:c r="F56" s="10" t="str">
+        <x:v>CBD</x:v>
+      </x:c>
+      <x:c r="G56" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H56" s="14" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I56" s="10" t="str">
+        <x:v>9.8</x:v>
+      </x:c>
+      <x:c r="J56" s="10" t="str">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="K56" s="12" t="str">
+        <x:v>CBD-rich infused kief built for a mellow, clear-headed session, with earthy pine running through it.</x:v>
+      </x:c>
+      <x:c r="L56" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+      <x:c r="M56" s="12" t="str">
+        <x:v>Pinene</x:v>
+      </x:c>
+      <x:c r="N56" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="10" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B57" s="10" t="str">
+        <x:v>Passion Flower</x:v>
+      </x:c>
+      <x:c r="C57" s="10" t="str">
+        <x:v>Rainbow Belts</x:v>
+      </x:c>
+      <x:c r="D57" s="10" t="str">
+        <x:v>Kief</x:v>
+      </x:c>
+      <x:c r="E57" s="10" t="str">
+        <x:v>Infused Kief</x:v>
+      </x:c>
+      <x:c r="F57" s="10" t="str">
+        <x:v>Hybrid</x:v>
+      </x:c>
+      <x:c r="G57" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H57" s="14" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I57" s="10" t="str">
+        <x:v>55.1</x:v>
+      </x:c>
+      <x:c r="J57" s="10" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K57" s="12" t="str">
+        <x:v>Terpene-enhanced kief that keeps Rainbow Belts' candied citrus and peppery finish intact.</x:v>
+      </x:c>
+      <x:c r="L57" s="12" t="str">
+        <x:v>Limonene</x:v>
+      </x:c>
+      <x:c r="M57" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+      <x:c r="N57" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="10" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B58" s="10" t="str">
+        <x:v>Skagit Organics</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="str">
+        <x:v>Blue Dream</x:v>
+      </x:c>
+      <x:c r="D58" s="10" t="str">
+        <x:v>RSO</x:v>
+      </x:c>
+      <x:c r="E58" s="10" t="str">
+        <x:v>Oil Syringe</x:v>
+      </x:c>
+      <x:c r="F58" s="10" t="str">
+        <x:v>Hybrid</x:v>
+      </x:c>
+      <x:c r="G58" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H58" s="14" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I58" s="10" t="str">
+        <x:v>72.5</x:v>
+      </x:c>
+      <x:c r="J58" s="10" t="str">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="K58" s="12" t="str">
+        <x:v>Unrefined full-spectrum extract in a measured syringe, earthy and pine-heavy. Start small.</x:v>
+      </x:c>
+      <x:c r="L58" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+      <x:c r="M58" s="12" t="str">
+        <x:v>Pinene</x:v>
+      </x:c>
+      <x:c r="N58" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="10" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B59" s="10" t="str">
+        <x:v>Buddies</x:v>
+      </x:c>
+      <x:c r="C59" s="10" t="str">
+        <x:v>Harlequin</x:v>
+      </x:c>
+      <x:c r="D59" s="10" t="str">
+        <x:v>RSO</x:v>
+      </x:c>
+      <x:c r="E59" s="10" t="str">
+        <x:v>Oil Syringe</x:v>
+      </x:c>
+      <x:c r="F59" s="10" t="str">
+        <x:v>CBD</x:v>
+      </x:c>
+      <x:c r="G59" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I59" s="10" t="str">
+        <x:v>32.4</x:v>
+      </x:c>
+      <x:c r="J59" s="10" t="str">
+        <x:v>31.8</x:v>
+      </x:c>
+      <x:c r="K59" s="12" t="str">
+        <x:v>Balanced full-spectrum RSO for measured, clear-headed relief, with a soft herbal-pine profile.</x:v>
+      </x:c>
+      <x:c r="L59" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+      <x:c r="M59" s="12" t="str">
+        <x:v>Pinene</x:v>
+      </x:c>
+      <x:c r="N59" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="10" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B60" s="10" t="str">
+        <x:v>Heylo</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="str">
+        <x:v>Wedding Cake</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="str">
+        <x:v>RSO</x:v>
+      </x:c>
+      <x:c r="E60" s="10" t="str">
+        <x:v>Applicator</x:v>
+      </x:c>
+      <x:c r="F60" s="10" t="str">
+        <x:v>Indica Hybrid</x:v>
+      </x:c>
+      <x:c r="G60" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H60" s="14" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I60" s="10" t="str">
+        <x:v>68.9</x:v>
+      </x:c>
+      <x:c r="J60" s="10" t="str">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="K60" s="12" t="str">
+        <x:v>Full-spectrum oil in a dosing applicator, rich and dessert-sweet with a peppery back end.</x:v>
+      </x:c>
+      <x:c r="L60" s="12" t="str">
+        <x:v>Limonene</x:v>
+      </x:c>
+      <x:c r="M60" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+      <x:c r="N60" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="10" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B61" s="10" t="str">
+        <x:v>Skagit Organics</x:v>
+      </x:c>
+      <x:c r="C61" s="10" t="str">
+        <x:v>Lifter</x:v>
+      </x:c>
+      <x:c r="D61" s="10" t="str">
+        <x:v>RSO</x:v>
+      </x:c>
+      <x:c r="E61" s="10" t="str">
+        <x:v>Applicator</x:v>
+      </x:c>
+      <x:c r="F61" s="10" t="str">
+        <x:v>CBD</x:v>
+      </x:c>
+      <x:c r="G61" s="10" t="str">
+        <x:v>1g</x:v>
+      </x:c>
+      <x:c r="H61" s="14" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I61" s="10" t="str">
+        <x:v>18.2</x:v>
+      </x:c>
+      <x:c r="J61" s="10" t="str">
+        <x:v>44.6</x:v>
+      </x:c>
+      <x:c r="K61" s="12" t="str">
+        <x:v>CBD-dominant full-spectrum oil in an applicator, herbal and lightly citric, made for daytime relief.</x:v>
+      </x:c>
+      <x:c r="L61" s="12" t="str">
+        <x:v>Myrcene</x:v>
+      </x:c>
+      <x:c r="M61" s="12" t="str">
+        <x:v>Caryophyllene</x:v>
+      </x:c>
+      <x:c r="N61" s="12" t="str">
+        <x:v>Pinene</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
